--- a/2026 New/results_ols_interactions.xlsx
+++ b/2026 New/results_ols_interactions.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f12debbb769dbfe/Database/GRIP/2026 New/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_4CE3745C4872A2897182020AFC15693F50D3AEFB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{657CCAF8-0B4D-4844-A73D-7608B39206B3}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_README" sheetId="1" r:id="rId1"/>
@@ -18,12 +24,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_PROFIT_MANUFACTURING'!$A$1:$J$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_INTERACTION_SUMMARY'!$A$1:$Q$49</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1204">
   <si>
     <t>item</t>
   </si>
@@ -4636,12 +4642,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="[&lt;0.0001]&quot;&lt;0.0001&quot;;0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4659,6 +4665,19 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -4689,7 +4708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4700,19 +4719,36 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4750,7 +4786,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4784,6 +4820,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4818,9 +4855,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4993,18 +5031,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="100.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="36" customHeight="1">
+    <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5012,7 +5050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" customHeight="1">
+    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -5020,7 +5058,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1">
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -5028,7 +5066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" customHeight="1">
+    <row r="4" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -5036,7 +5074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="45" customHeight="1">
+    <row r="5" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -5044,7 +5082,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" customHeight="1">
+    <row r="6" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -5052,7 +5090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="60" customHeight="1">
+    <row r="7" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -5060,7 +5098,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="45" customHeight="1">
+    <row r="8" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -5068,7 +5106,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="45" customHeight="1">
+    <row r="9" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -5076,7 +5114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1">
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -5084,7 +5122,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -5092,7 +5130,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="60" customHeight="1">
+    <row r="12" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -5100,7 +5138,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="45" customHeight="1">
+    <row r="13" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -5108,7 +5146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="60" customHeight="1">
+    <row r="14" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -5116,7 +5154,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="45" customHeight="1">
+    <row r="15" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -5124,7 +5162,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="45" customHeight="1">
+    <row r="16" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -5132,7 +5170,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="45" customHeight="1">
+    <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -5140,7 +5178,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -5148,7 +5186,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="45" customHeight="1">
+    <row r="19" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -5156,7 +5194,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="45" customHeight="1">
+    <row r="20" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -5164,7 +5202,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1">
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
@@ -5172,7 +5210,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="45" customHeight="1">
+    <row r="22" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
@@ -5180,7 +5218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="45" customHeight="1">
+    <row r="23" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -5189,5220 +5227,5249 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B23"/>
+  <autoFilter ref="A1:B23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1">
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
   <dimension ref="A1:J103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" style="1" customWidth="1"/>
-    <col min="3" max="10" width="24.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="24" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="24" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="24" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="24" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="24" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="36.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="42" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" ht="42.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="42" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:10" ht="42.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="8" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="8" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="8" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="8" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="8" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="8" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="8" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="8" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="8" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="8" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="8" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="8" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="8" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="8" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="8" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="8" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="8" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="8" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" customHeight="1">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="8" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="8" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="8" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="8" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" s="8" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" s="8" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="8" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="8" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="42" customHeight="1">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:10" ht="42.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="42" customHeight="1">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:10" ht="42.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30" customHeight="1">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="8" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="30" customHeight="1">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="8" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" customHeight="1">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" s="8" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" s="8" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30" customHeight="1">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" s="8" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" s="8" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" customHeight="1">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" s="8" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="30" customHeight="1">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" s="8" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" customHeight="1">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="8" t="s">
         <v>665</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" s="8" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" s="8" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" customHeight="1">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" s="8" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="8" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" s="8" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" customHeight="1">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="8" t="s">
         <v>670</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" s="8" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" customHeight="1">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" s="8" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" customHeight="1">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" s="8" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" customHeight="1">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" s="8" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="30" customHeight="1">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="8" t="s">
         <v>674</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" s="8" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30" customHeight="1">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="8" t="s">
         <v>587</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" s="8" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="30" customHeight="1">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" s="8" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="30" customHeight="1">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="8" t="s">
         <v>677</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" s="8" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="30" customHeight="1">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="8" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="30" customHeight="1">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" s="8" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="18" customHeight="1">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" s="8" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="18" customHeight="1">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" s="8" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="18" customHeight="1">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" s="8" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="42" customHeight="1">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:10" ht="42.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="42" customHeight="1">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:10" ht="42.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="30" customHeight="1">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" s="8" t="s">
         <v>682</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" s="8" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="30" customHeight="1">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="J61" s="8" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="30" customHeight="1">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I62" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="J62" s="8" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="30" customHeight="1">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="I63" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="J63" s="8" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="30" customHeight="1">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I64" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="J64" s="8" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="30" customHeight="1">
-      <c r="A65" s="1" t="s">
+    <row r="65" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I65" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="J65" s="8" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="30" customHeight="1">
-      <c r="A66" s="1" t="s">
+    <row r="66" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="J66" s="8" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="30" customHeight="1">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="J67" s="8" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="30" customHeight="1">
-      <c r="A68" s="1" t="s">
+    <row r="68" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="J68" s="8" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="30" customHeight="1">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G69" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="I69" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="J69" s="8" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="30" customHeight="1">
-      <c r="A70" s="1" t="s">
+    <row r="70" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="I70" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="J70" s="8" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="30" customHeight="1">
-      <c r="A71" s="1" t="s">
+    <row r="71" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="I71" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="J71" s="8" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="30" customHeight="1">
-      <c r="A72" s="1" t="s">
+    <row r="72" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I72" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="J72" s="8" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="30" customHeight="1">
-      <c r="A73" s="1" t="s">
+    <row r="73" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="8" t="s">
         <v>693</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="J73" s="8" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="30" customHeight="1">
-      <c r="A74" s="1" t="s">
+    <row r="74" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G74" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I74" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="J74" s="8" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="30" customHeight="1">
-      <c r="A75" s="1" t="s">
+    <row r="75" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G75" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="I75" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="J75" s="8" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="30" customHeight="1">
-      <c r="A76" s="1" t="s">
+    <row r="76" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G76" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="I76" s="8" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="30" customHeight="1">
-      <c r="A77" s="1" t="s">
+    <row r="77" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="I77" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" s="8" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="18" customHeight="1">
-      <c r="A78" s="1" t="s">
+    <row r="78" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G78" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H78" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="I78" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="J78" s="8" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="18" customHeight="1">
-      <c r="A79" s="1" t="s">
+    <row r="79" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="G79" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="I79" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="J79" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="18" customHeight="1">
-      <c r="A80" s="1" t="s">
+    <row r="80" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G80" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H80" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I80" s="8" t="s">
         <v>699</v>
       </c>
-      <c r="J80" s="1" t="s">
+      <c r="J80" s="8" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="42" customHeight="1">
-      <c r="A81" s="1" t="s">
+    <row r="81" spans="1:10" ht="42.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="I81" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="J81" s="1" t="s">
+      <c r="J81" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="42" customHeight="1">
-      <c r="A82" s="1" t="s">
+    <row r="82" spans="1:10" ht="42.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G82" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I82" s="1" t="s">
+      <c r="I82" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="J82" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="30" customHeight="1">
-      <c r="A83" s="1" t="s">
+    <row r="83" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G83" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="I83" s="8" t="s">
         <v>700</v>
       </c>
-      <c r="J83" s="1" t="s">
+      <c r="J83" s="8" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="30" customHeight="1">
-      <c r="A84" s="1" t="s">
+    <row r="84" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="G84" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="H84" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="I84" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="J84" s="1" t="s">
+      <c r="J84" s="8" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="30" customHeight="1">
-      <c r="A85" s="1" t="s">
+    <row r="85" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="G85" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="H85" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="I85" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="J85" s="8" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="30" customHeight="1">
-      <c r="A86" s="1" t="s">
+    <row r="86" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="G86" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="H86" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="I86" s="1" t="s">
+      <c r="I86" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="J86" s="8" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="30" customHeight="1">
-      <c r="A87" s="1" t="s">
+    <row r="87" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G87" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="H87" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="I87" s="1" t="s">
+      <c r="I87" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="J87" s="1" t="s">
+      <c r="J87" s="8" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="30" customHeight="1">
-      <c r="A88" s="1" t="s">
+    <row r="88" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="G88" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H88" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="I88" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="J88" s="8" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="30" customHeight="1">
-      <c r="A89" s="1" t="s">
+    <row r="89" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="F89" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="G89" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="I89" s="1" t="s">
+      <c r="I89" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="J89" s="1" t="s">
+      <c r="J89" s="8" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="30" customHeight="1">
-      <c r="A90" s="1" t="s">
+    <row r="90" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="G90" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="I90" s="1" t="s">
+      <c r="I90" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="J90" s="1" t="s">
+      <c r="J90" s="8" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="30" customHeight="1">
-      <c r="A91" s="1" t="s">
+    <row r="91" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="G91" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="I91" s="1" t="s">
+      <c r="I91" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="J91" s="1" t="s">
+      <c r="J91" s="8" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="30" customHeight="1">
-      <c r="A92" s="1" t="s">
+    <row r="92" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F92" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="G92" s="1" t="s">
+      <c r="G92" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="H92" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="I92" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="J92" s="1" t="s">
+      <c r="J92" s="8" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="30" customHeight="1">
-      <c r="A93" s="1" t="s">
+    <row r="93" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="G93" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H93" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="I93" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="J93" s="1" t="s">
+      <c r="J93" s="8" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="30" customHeight="1">
-      <c r="A94" s="1" t="s">
+    <row r="94" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F94" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="G94" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H94" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="I94" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="J94" s="1" t="s">
+      <c r="J94" s="8" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="30" customHeight="1">
-      <c r="A95" s="1" t="s">
+    <row r="95" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E95" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F95" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="G95" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H95" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="I95" s="1" t="s">
+      <c r="I95" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="J95" s="1" t="s">
+      <c r="J95" s="8" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="30" customHeight="1">
-      <c r="A96" s="1" t="s">
+    <row r="96" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="E96" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="F96" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="G96" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="H96" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="I96" s="8" t="s">
         <v>713</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="J96" s="8" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="30" customHeight="1">
-      <c r="A97" s="1" t="s">
+    <row r="97" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E97" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="F97" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="G97" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H97" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="I97" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="J97" s="8" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="30" customHeight="1">
-      <c r="A98" s="1" t="s">
+    <row r="98" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="G98" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="I98" s="8" t="s">
         <v>715</v>
       </c>
-      <c r="J98" s="1" t="s">
+      <c r="J98" s="8" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="30" customHeight="1">
-      <c r="A99" s="1" t="s">
+    <row r="99" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E99" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="G99" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H99" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="I99" s="8" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="30" customHeight="1">
-      <c r="A100" s="1" t="s">
+    <row r="100" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="G100" s="1" t="s">
+      <c r="G100" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H100" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I100" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="J100" s="1" t="s">
+      <c r="J100" s="8" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="18" customHeight="1">
-      <c r="A101" s="1" t="s">
+    <row r="101" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F101" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G101" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H101" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I101" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="J101" s="1" t="s">
+      <c r="J101" s="8" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="18" customHeight="1">
-      <c r="A102" s="1" t="s">
+    <row r="102" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="F102" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="G102" s="1" t="s">
+      <c r="G102" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="H102" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="I102" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="J102" s="1" t="s">
+      <c r="J102" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="18" customHeight="1">
-      <c r="A103" s="1" t="s">
+    <row r="103" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F103" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="G103" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="H103" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I103" s="8" t="s">
         <v>719</v>
       </c>
-      <c r="J103" s="1" t="s">
+      <c r="J103" s="8" t="s">
         <v>800</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J103"/>
+  <autoFilter ref="A1:J103" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="RANK2019"/>
+        <filter val="RANK2019_MANUFACTURING"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1">
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
   <dimension ref="A1:J59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" style="1" customWidth="1"/>
-    <col min="3" max="10" width="24.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="36.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="42" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" ht="42.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="42" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:10" ht="42.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="8" t="s">
         <v>897</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="8" t="s">
         <v>1089</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="8" t="s">
         <v>1137</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="8" t="s">
         <v>803</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="8" t="s">
         <v>1041</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="8" t="s">
         <v>1138</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>804</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="8" t="s">
         <v>946</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="8" t="s">
         <v>1042</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="8" t="s">
         <v>1139</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="8" t="s">
         <v>947</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="8" t="s">
         <v>993</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="8" t="s">
         <v>1092</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="8" t="s">
         <v>1140</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="8" t="s">
         <v>1093</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="8" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="8" t="s">
         <v>995</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="8" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="7" t="s">
         <v>801</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="8" t="s">
         <v>996</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="8" t="s">
         <v>1094</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="8" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="8" t="s">
         <v>997</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="8" t="s">
         <v>1047</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="8" t="s">
         <v>1095</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="8" t="s">
         <v>1144</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="8" t="s">
         <v>998</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="8" t="s">
         <v>1096</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="8" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="8" t="s">
         <v>1097</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="8" t="s">
         <v>1146</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="8" t="s">
         <v>860</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="8" t="s">
         <v>1050</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="8" t="s">
         <v>1098</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="8" t="s">
         <v>1147</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="8" t="s">
         <v>861</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="8" t="s">
         <v>954</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="8" t="s">
         <v>1001</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="8" t="s">
         <v>1099</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="8" t="s">
         <v>1148</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="8" t="s">
         <v>862</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="8" t="s">
         <v>955</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="8" t="s">
         <v>1002</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="8" t="s">
         <v>1052</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="8" t="s">
         <v>1100</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="8" t="s">
         <v>1149</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="8" t="s">
         <v>1003</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="8" t="s">
         <v>1053</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="8" t="s">
         <v>1101</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="8" t="s">
         <v>1150</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="8" t="s">
         <v>1004</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="8" t="s">
         <v>1054</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="8" t="s">
         <v>1102</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="8" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="8" t="s">
         <v>958</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="8" t="s">
         <v>1005</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="8" t="s">
         <v>1055</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="8" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="8" t="s">
         <v>866</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="8" t="s">
         <v>959</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="8" t="s">
         <v>1056</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="8" t="s">
         <v>1103</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="8" t="s">
         <v>1153</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="8" t="s">
         <v>818</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="8" t="s">
         <v>867</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="8" t="s">
         <v>1007</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="8" t="s">
         <v>1057</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="8" t="s">
         <v>1104</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="8" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" customHeight="1">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="8" t="s">
         <v>961</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="8" t="s">
         <v>1008</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="8" t="s">
         <v>1058</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="8" t="s">
         <v>1105</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="8" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="8" t="s">
         <v>820</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="8" t="s">
         <v>962</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="8" t="s">
         <v>1059</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="8" t="s">
         <v>1106</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="8" t="s">
         <v>1156</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="8" t="s">
         <v>821</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="8" t="s">
         <v>963</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="8" t="s">
         <v>1060</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="8" t="s">
         <v>1107</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="8" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="8" t="s">
         <v>822</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="8" t="s">
         <v>964</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="8" t="s">
         <v>1061</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="8" t="s">
         <v>1108</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="8" t="s">
         <v>1158</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="8" t="s">
         <v>872</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="8" t="s">
         <v>1062</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="8" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:10" ht="30.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="8" t="s">
         <v>873</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="8" t="s">
         <v>1013</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="8" t="s">
         <v>1063</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="8" t="s">
         <v>1110</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" s="8" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="8" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="8" t="s">
         <v>1064</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="8" t="s">
         <v>1111</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="8" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:10" ht="18.0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="8" t="s">
         <v>920</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="8" t="s">
         <v>966</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="8" t="s">
         <v>1065</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="8" t="s">
         <v>1112</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="8" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="42" customHeight="1">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:10" ht="42.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="42" customHeight="1">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:10" ht="42.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="30" customHeight="1">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="8" t="s">
         <v>967</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="8" t="s">
         <v>1066</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="8" t="s">
         <v>1113</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="8" t="s">
         <v>1161</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" customHeight="1">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="8" t="s">
         <v>1016</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="8" t="s">
         <v>1067</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="8" t="s">
         <v>1114</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" s="8" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" s="8" t="s">
         <v>1163</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30" customHeight="1">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="8" t="s">
         <v>924</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="8" t="s">
         <v>1069</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="8" t="s">
         <v>1115</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" s="8" t="s">
         <v>1164</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="8" t="s">
         <v>970</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="8" t="s">
         <v>1019</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="8" t="s">
         <v>1070</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="8" t="s">
         <v>1116</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" s="8" t="s">
         <v>1165</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" customHeight="1">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="8" t="s">
         <v>1020</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="8" t="s">
         <v>1117</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" s="8" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="30" customHeight="1">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="7" t="s">
         <v>801</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="8" t="s">
         <v>880</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="8" t="s">
         <v>1118</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" s="8" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" customHeight="1">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="8" t="s">
         <v>881</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="8" t="s">
         <v>927</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="8" t="s">
         <v>1022</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="8" t="s">
         <v>1119</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" s="8" t="s">
         <v>1167</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="8" t="s">
         <v>834</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="8" t="s">
         <v>882</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="8" t="s">
         <v>928</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="8" t="s">
         <v>1073</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" s="8" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" customHeight="1">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="8" t="s">
         <v>929</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="8" t="s">
         <v>1024</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="8" t="s">
         <v>1074</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="8" t="s">
         <v>1121</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" s="8" t="s">
         <v>1169</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="8" t="s">
         <v>1025</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="8" t="s">
         <v>1122</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="8" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="8" t="s">
         <v>885</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="8" t="s">
         <v>1026</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="8" t="s">
         <v>1076</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" s="8" t="s">
         <v>1171</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" customHeight="1">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="8" t="s">
         <v>1027</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="8" t="s">
         <v>1077</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" s="8" t="s">
         <v>1172</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" customHeight="1">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="8" t="s">
         <v>887</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="8" t="s">
         <v>933</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="8" t="s">
         <v>1078</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="8" t="s">
         <v>1125</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" s="8" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" customHeight="1">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="8" t="s">
         <v>1029</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="8" t="s">
         <v>1079</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" s="8" t="s">
         <v>1174</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" customHeight="1">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="8" t="s">
         <v>1030</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="8" t="s">
         <v>1080</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="8" t="s">
         <v>1127</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" s="8" t="s">
         <v>1175</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="30" customHeight="1">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="8" t="s">
         <v>1081</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="8" t="s">
         <v>1128</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" s="8" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30" customHeight="1">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="8" t="s">
         <v>1032</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="8" t="s">
         <v>1082</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" s="8" t="s">
         <v>1177</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="30" customHeight="1">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="8" t="s">
         <v>983</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="8" t="s">
         <v>1033</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" s="8" t="s">
         <v>1178</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="30" customHeight="1">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="8" t="s">
         <v>1034</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="8" t="s">
         <v>1084</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" s="8" t="s">
         <v>1179</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="30" customHeight="1">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="8" t="s">
         <v>1035</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="8" t="s">
         <v>1085</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="8" t="s">
         <v>1132</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="J53" s="8" t="s">
         <v>1180</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="30" customHeight="1">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="8" t="s">
         <v>1036</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" s="8" t="s">
         <v>1086</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" s="8" t="s">
         <v>1181</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="30" customHeight="1">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="8" t="s">
         <v>1037</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="8" t="s">
         <v>1087</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="8" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="30" customHeight="1">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:10" ht="30.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="8" t="s">
         <v>987</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="8" t="s">
         <v>1038</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" s="8" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="18" customHeight="1">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" s="8" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="18" customHeight="1">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" s="8" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="18" customHeight="1">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:10" ht="18.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="8" t="s">
         <v>989</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="8" t="s">
         <v>1039</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="8" t="s">
         <v>1136</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" s="8" t="s">
         <v>425</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J59"/>
+  <autoFilter ref="A1:J59" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="RANK2019"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
   <dimension ref="A1:Q49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="28.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="5" customWidth="1"/>
-    <col min="12" max="16" width="21.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="28.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="28.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" style="5" customWidth="1"/>
+    <col min="12" max="16" width="21.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="48" customHeight="1">
+    <row r="1" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>1183</v>
       </c>
@@ -10455,7 +10522,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10469,28 +10536,28 @@
         <v>1202</v>
       </c>
       <c r="I2" s="3">
-        <v>0.04440315536015214</v>
+        <v>4.4403155360152137E-2</v>
       </c>
       <c r="J2" s="4">
-        <v>0.01215953734794026</v>
+        <v>1.215953734794026E-2</v>
       </c>
       <c r="K2" s="5">
         <v>2385</v>
       </c>
       <c r="L2" s="3">
-        <v>0.3191704110654772</v>
+        <v>0.31917041106547722</v>
       </c>
       <c r="M2" s="3">
-        <v>0.312829068577518</v>
+        <v>0.31282906857751802</v>
       </c>
       <c r="N2" s="3">
-        <v>0.311288628691852</v>
+        <v>0.31128862869185198</v>
       </c>
       <c r="Q2" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -10504,28 +10571,28 @@
         <v>1202</v>
       </c>
       <c r="I3" s="3">
-        <v>-0.07032059001508713</v>
+        <v>-7.0320590015087128E-2</v>
       </c>
       <c r="J3" s="4">
-        <v>0.0002223880833502543</v>
+        <v>2.2238808335025431E-4</v>
       </c>
       <c r="K3" s="5">
         <v>2426</v>
       </c>
       <c r="L3" s="3">
-        <v>0.1955298853383023</v>
+        <v>0.19552988533830229</v>
       </c>
       <c r="M3" s="3">
-        <v>0.1881647823326605</v>
+        <v>0.18816478233266051</v>
       </c>
       <c r="N3" s="3">
-        <v>0.1838849595365291</v>
+        <v>0.18388495953652911</v>
       </c>
       <c r="Q3" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -10539,16 +10606,16 @@
         <v>1202</v>
       </c>
       <c r="I4" s="3">
-        <v>0.05835796428973022</v>
+        <v>5.8357964289730217E-2</v>
       </c>
       <c r="J4" s="4">
-        <v>0.002463959176840373</v>
+        <v>2.463959176840373E-3</v>
       </c>
       <c r="K4" s="5">
         <v>2438</v>
       </c>
       <c r="L4" s="3">
-        <v>0.1679300222129329</v>
+        <v>0.16793002221293291</v>
       </c>
       <c r="M4" s="3">
         <v>0.1603500886678747</v>
@@ -10560,7 +10627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -10574,10 +10641,10 @@
         <v>1202</v>
       </c>
       <c r="I5" s="3">
-        <v>-0.03450668221058664</v>
+        <v>-3.4506682210586642E-2</v>
       </c>
       <c r="J5" s="4">
-        <v>0.05594327655366511</v>
+        <v>5.5943276553665107E-2</v>
       </c>
       <c r="K5" s="5">
         <v>2423</v>
@@ -10586,16 +10653,16 @@
         <v>0.2975540844037734</v>
       </c>
       <c r="M5" s="3">
-        <v>0.2914102425764011</v>
+        <v>0.29141024257640108</v>
       </c>
       <c r="N5" s="3">
-        <v>0.2906263426476376</v>
+        <v>0.29062634264763759</v>
       </c>
       <c r="Q5" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -10609,10 +10676,10 @@
         <v>1203</v>
       </c>
       <c r="I6" s="3">
-        <v>0.03407948812652559</v>
+        <v>3.4079488126525587E-2</v>
       </c>
       <c r="J6" s="4">
-        <v>0.0929001620898179</v>
+        <v>9.2900162089817898E-2</v>
       </c>
       <c r="K6" s="5">
         <v>2385</v>
@@ -10621,16 +10688,16 @@
         <v>0.1062416992463243</v>
       </c>
       <c r="M6" s="3">
-        <v>0.09791710880746707</v>
+        <v>9.7917108807467068E-2</v>
       </c>
       <c r="N6" s="3">
-        <v>0.09722015191324307</v>
+        <v>9.7220151913243069E-2</v>
       </c>
       <c r="Q6" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -10644,28 +10711,28 @@
         <v>1203</v>
       </c>
       <c r="I7" s="3">
-        <v>0.01210934653981012</v>
+        <v>1.210934653981012E-2</v>
       </c>
       <c r="J7" s="4">
-        <v>0.5263662497832989</v>
+        <v>0.52636624978329893</v>
       </c>
       <c r="K7" s="5">
         <v>2426</v>
       </c>
       <c r="L7" s="3">
-        <v>0.1876255247158899</v>
+        <v>0.18762552471588989</v>
       </c>
       <c r="M7" s="3">
-        <v>0.1801880555289359</v>
+        <v>0.18018805552893591</v>
       </c>
       <c r="N7" s="3">
-        <v>0.1803921495660886</v>
+        <v>0.18039214956608859</v>
       </c>
       <c r="Q7" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -10679,28 +10746,28 @@
         <v>1203</v>
       </c>
       <c r="I8" s="3">
-        <v>-0.03674871666231081</v>
+        <v>-3.6748716662310811E-2</v>
       </c>
       <c r="J8" s="4">
-        <v>0.05945558649789923</v>
+        <v>5.9455586497899227E-2</v>
       </c>
       <c r="K8" s="5">
         <v>2438</v>
       </c>
       <c r="L8" s="3">
-        <v>0.1475884579019018</v>
+        <v>0.14758845790190181</v>
       </c>
       <c r="M8" s="3">
-        <v>0.1398232181809254</v>
+        <v>0.13982321818092541</v>
       </c>
       <c r="N8" s="3">
-        <v>0.1389132476584458</v>
+        <v>0.13891324765844579</v>
       </c>
       <c r="Q8" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -10714,28 +10781,28 @@
         <v>1203</v>
       </c>
       <c r="I9" s="3">
-        <v>-0.0591261074807695</v>
+        <v>-5.9126107480769498E-2</v>
       </c>
       <c r="J9" s="4">
-        <v>0.001230769813746057</v>
+        <v>1.2307698137460569E-3</v>
       </c>
       <c r="K9" s="5">
         <v>2423</v>
       </c>
       <c r="L9" s="3">
-        <v>0.2794904209175197</v>
+        <v>0.27949042091751969</v>
       </c>
       <c r="M9" s="3">
-        <v>0.2731885878643202</v>
+        <v>0.27318858786432021</v>
       </c>
       <c r="N9" s="3">
-        <v>0.2703235522227802</v>
+        <v>0.27032355222278021</v>
       </c>
       <c r="Q9" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -10749,28 +10816,28 @@
         <v>1202</v>
       </c>
       <c r="I10" s="3">
-        <v>-0.03282006265101559</v>
+        <v>-3.2820062651015593E-2</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1653680596337462</v>
+        <v>0.16536805963374621</v>
       </c>
       <c r="K10" s="5">
         <v>1786</v>
       </c>
       <c r="L10" s="3">
-        <v>0.06977978046897759</v>
+        <v>6.9779780468977592E-2</v>
       </c>
       <c r="M10" s="3">
-        <v>0.0581718140312677</v>
+        <v>5.8171814031267699E-2</v>
       </c>
       <c r="N10" s="3">
-        <v>0.05767738798451127</v>
+        <v>5.7677387984511268E-2</v>
       </c>
       <c r="Q10" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -10784,7 +10851,7 @@
         <v>1202</v>
       </c>
       <c r="I11" s="3">
-        <v>-0.0135074027136361</v>
+        <v>-1.35074027136361E-2</v>
       </c>
       <c r="J11" s="4">
         <v>0.5601498925649282</v>
@@ -10793,19 +10860,19 @@
         <v>1791</v>
       </c>
       <c r="L11" s="3">
-        <v>0.1051598249287476</v>
+        <v>0.10515982492874761</v>
       </c>
       <c r="M11" s="3">
-        <v>0.09402493587243121</v>
+        <v>9.4024935872431215E-2</v>
       </c>
       <c r="N11" s="3">
-        <v>0.09436316654183807</v>
+        <v>9.4363166541838073E-2</v>
       </c>
       <c r="Q11" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -10819,19 +10886,19 @@
         <v>1202</v>
       </c>
       <c r="I12" s="3">
-        <v>-0.04806236669017266</v>
+        <v>-4.8062366690172657E-2</v>
       </c>
       <c r="J12" s="4">
-        <v>0.03386160269912376</v>
+        <v>3.3861602699123763E-2</v>
       </c>
       <c r="K12" s="5">
         <v>1795</v>
       </c>
       <c r="L12" s="3">
-        <v>0.1422420189790249</v>
+        <v>0.14224201897902489</v>
       </c>
       <c r="M12" s="3">
-        <v>0.1315926535261686</v>
+        <v>0.13159265352616861</v>
       </c>
       <c r="N12" s="3">
         <v>0.1298741205893674</v>
@@ -10840,7 +10907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -10854,28 +10921,28 @@
         <v>1202</v>
       </c>
       <c r="I13" s="3">
-        <v>-0.03906205526077444</v>
+        <v>-3.9062055260774442E-2</v>
       </c>
       <c r="J13" s="4">
-        <v>0.09804753939395379</v>
+        <v>9.8047539393953789E-2</v>
       </c>
       <c r="K13" s="5">
         <v>1794</v>
       </c>
       <c r="L13" s="3">
-        <v>0.06641302220475431</v>
+        <v>6.6413022204754313E-2</v>
       </c>
       <c r="M13" s="3">
-        <v>0.05534906817896401</v>
+        <v>5.5349068178964012E-2</v>
       </c>
       <c r="N13" s="3">
-        <v>0.0544220491351709</v>
+        <v>5.4422049135170902E-2</v>
       </c>
       <c r="Q13" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -10889,28 +10956,28 @@
         <v>1203</v>
       </c>
       <c r="I14" s="3">
-        <v>-0.03960305077089641</v>
+        <v>-3.960305077089641E-2</v>
       </c>
       <c r="J14" s="4">
-        <v>0.09357079783274605</v>
+        <v>9.357079783274605E-2</v>
       </c>
       <c r="K14" s="5">
         <v>1786</v>
       </c>
       <c r="L14" s="3">
-        <v>0.07323832443631362</v>
+        <v>7.3238324436313618E-2</v>
       </c>
       <c r="M14" s="3">
-        <v>0.0616735162330232</v>
+        <v>6.1673516233023203E-2</v>
       </c>
       <c r="N14" s="3">
-        <v>0.06070812207743037</v>
+        <v>6.0708122077430371E-2</v>
       </c>
       <c r="Q14" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -10924,28 +10991,28 @@
         <v>1203</v>
       </c>
       <c r="I15" s="3">
-        <v>-0.0204540926676188</v>
+        <v>-2.0454092667618801E-2</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3687455682004328</v>
+        <v>0.36874556820043281</v>
       </c>
       <c r="K15" s="5">
         <v>1791</v>
       </c>
       <c r="L15" s="3">
-        <v>0.1379689326417212</v>
+        <v>0.13796893264172119</v>
       </c>
       <c r="M15" s="3">
-        <v>0.1272423017130548</v>
+        <v>0.12724230171305481</v>
       </c>
       <c r="N15" s="3">
-        <v>0.1273368789217753</v>
+        <v>0.12733687892177531</v>
       </c>
       <c r="Q15" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -10959,19 +11026,19 @@
         <v>1203</v>
       </c>
       <c r="I16" s="3">
-        <v>-0.04722007603211172</v>
+        <v>-4.7220076032111723E-2</v>
       </c>
       <c r="J16" s="4">
-        <v>0.03231606471003192</v>
+        <v>3.2316064710031921E-2</v>
       </c>
       <c r="K16" s="5">
         <v>1795</v>
       </c>
       <c r="L16" s="3">
-        <v>0.1865132544314994</v>
+        <v>0.18651325443149941</v>
       </c>
       <c r="M16" s="3">
-        <v>0.1764135318567212</v>
+        <v>0.17641353185672121</v>
       </c>
       <c r="N16" s="3">
         <v>0.1747464427034052</v>
@@ -10980,7 +11047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -10994,28 +11061,28 @@
         <v>1203</v>
       </c>
       <c r="I17" s="3">
-        <v>-0.04197697681800826</v>
+        <v>-4.1976976818008258E-2</v>
       </c>
       <c r="J17" s="4">
-        <v>0.07521210161117253</v>
+        <v>7.5212101611172533E-2</v>
       </c>
       <c r="K17" s="5">
         <v>1794</v>
       </c>
       <c r="L17" s="3">
-        <v>0.0679099645785517</v>
+        <v>6.7909964578551696E-2</v>
       </c>
       <c r="M17" s="3">
-        <v>0.056863750840487</v>
+        <v>5.6863750840486997E-2</v>
       </c>
       <c r="N17" s="3">
-        <v>0.05570987700212515</v>
+        <v>5.5709877002125152E-2</v>
       </c>
       <c r="Q17" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -11029,10 +11096,10 @@
         <v>1202</v>
       </c>
       <c r="I18" s="3">
-        <v>0.05296859890219112</v>
+        <v>5.2968598902191119E-2</v>
       </c>
       <c r="J18" s="4">
-        <v>0.09818643811389317</v>
+        <v>9.8186438113893174E-2</v>
       </c>
       <c r="K18" s="5">
         <v>979</v>
@@ -11041,16 +11108,16 @@
         <v>0.1192645963402644</v>
       </c>
       <c r="M18" s="3">
-        <v>0.103684469532548</v>
+        <v>0.10368446953254799</v>
       </c>
       <c r="N18" s="3">
-        <v>0.1020632016912068</v>
+        <v>0.10206320169120681</v>
       </c>
       <c r="Q18" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -11064,28 +11131,28 @@
         <v>1202</v>
       </c>
       <c r="I19" s="3">
-        <v>-0.03562276336053761</v>
+        <v>-3.5622763360537608E-2</v>
       </c>
       <c r="J19" s="4">
-        <v>0.1954900704304368</v>
+        <v>0.19549007043043681</v>
       </c>
       <c r="K19" s="5">
         <v>995</v>
       </c>
       <c r="L19" s="3">
-        <v>0.2959171122806945</v>
+        <v>0.29591711228069451</v>
       </c>
       <c r="M19" s="3">
-        <v>0.2836659259027742</v>
+        <v>0.28366592590277417</v>
       </c>
       <c r="N19" s="3">
-        <v>0.2831692913374456</v>
+        <v>0.28316929133744562</v>
       </c>
       <c r="Q19" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -11099,28 +11166,28 @@
         <v>1202</v>
       </c>
       <c r="I20" s="3">
-        <v>0.0313231731118452</v>
+        <v>3.1323173111845203E-2</v>
       </c>
       <c r="J20" s="4">
-        <v>0.2849055251872548</v>
+        <v>0.28490552518725482</v>
       </c>
       <c r="K20" s="5">
         <v>1000</v>
       </c>
       <c r="L20" s="3">
-        <v>0.2931109872096745</v>
+        <v>0.29311098720967449</v>
       </c>
       <c r="M20" s="3">
-        <v>0.2808736010412066</v>
+        <v>0.28087360104120662</v>
       </c>
       <c r="N20" s="3">
-        <v>0.2807676786116514</v>
+        <v>0.28076767861165142</v>
       </c>
       <c r="Q20" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -11137,25 +11204,25 @@
         <v>0.1096053236772284</v>
       </c>
       <c r="J21" s="4">
-        <v>3.558812475152815E-05</v>
+        <v>3.5588124751528151E-5</v>
       </c>
       <c r="K21" s="5">
         <v>995</v>
       </c>
       <c r="L21" s="3">
-        <v>0.3919567392456783</v>
+        <v>0.39195673924567831</v>
       </c>
       <c r="M21" s="3">
-        <v>0.3820092012374277</v>
+        <v>0.38200920123742771</v>
       </c>
       <c r="N21" s="3">
-        <v>0.3717499187682636</v>
+        <v>0.37174991876826358</v>
       </c>
       <c r="Q21" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -11169,10 +11236,10 @@
         <v>1203</v>
       </c>
       <c r="I22" s="3">
-        <v>0.0603499659612425</v>
+        <v>6.0349965961242501E-2</v>
       </c>
       <c r="J22" s="4">
-        <v>0.05564405668612528</v>
+        <v>5.5644056686125279E-2</v>
       </c>
       <c r="K22" s="5">
         <v>979</v>
@@ -11181,16 +11248,16 @@
         <v>0.1467576421638008</v>
       </c>
       <c r="M22" s="3">
-        <v>0.1316638647619117</v>
+        <v>0.13166386476191169</v>
       </c>
       <c r="N22" s="3">
-        <v>0.1292523981509557</v>
+        <v>0.12925239815095571</v>
       </c>
       <c r="Q22" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -11204,28 +11271,28 @@
         <v>1203</v>
       </c>
       <c r="I23" s="3">
-        <v>0.03598775690516552</v>
+        <v>3.5987756905165522E-2</v>
       </c>
       <c r="J23" s="4">
-        <v>0.2189089394539624</v>
+        <v>0.21890893945396239</v>
       </c>
       <c r="K23" s="5">
         <v>995</v>
       </c>
       <c r="L23" s="3">
-        <v>0.2032662349614955</v>
+        <v>0.20326623496149551</v>
       </c>
       <c r="M23" s="3">
-        <v>0.1894029043518184</v>
+        <v>0.18940290435181839</v>
       </c>
       <c r="N23" s="3">
-        <v>0.1889773376669235</v>
+        <v>0.18897733766692351</v>
       </c>
       <c r="Q23" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -11239,7 +11306,7 @@
         <v>1203</v>
       </c>
       <c r="I24" s="3">
-        <v>0.01186161843781061</v>
+        <v>1.186161843781061E-2</v>
       </c>
       <c r="J24" s="4">
         <v>0.6951393096318681</v>
@@ -11251,7 +11318,7 @@
         <v>0.2448223184103834</v>
       </c>
       <c r="M24" s="3">
-        <v>0.2317489776904001</v>
+        <v>0.23174897769040009</v>
       </c>
       <c r="N24" s="3">
         <v>0.2324104174342034</v>
@@ -11260,7 +11327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -11274,19 +11341,19 @@
         <v>1203</v>
       </c>
       <c r="I25" s="3">
-        <v>0.09688733282441607</v>
+        <v>9.688733282441607E-2</v>
       </c>
       <c r="J25" s="4">
-        <v>0.0006691500819005695</v>
+        <v>6.6915008190056953E-4</v>
       </c>
       <c r="K25" s="5">
         <v>995</v>
       </c>
       <c r="L25" s="3">
-        <v>0.2962599947909116</v>
+        <v>0.29625999479091158</v>
       </c>
       <c r="M25" s="3">
-        <v>0.2847468658713355</v>
+        <v>0.28474686587133552</v>
       </c>
       <c r="N25" s="3">
         <v>0.2769676547753307</v>
@@ -11295,7 +11362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
@@ -11309,28 +11376,28 @@
         <v>1202</v>
       </c>
       <c r="I26" s="3">
-        <v>0.03409623631319002</v>
+        <v>3.4096236313190018E-2</v>
       </c>
       <c r="J26" s="4">
-        <v>0.3398874366538353</v>
+        <v>0.33988743665383531</v>
       </c>
       <c r="K26" s="5">
         <v>781</v>
       </c>
       <c r="L26" s="3">
-        <v>0.1069057205740691</v>
+        <v>0.10690572057406909</v>
       </c>
       <c r="M26" s="3">
-        <v>0.08700715864714803</v>
+        <v>8.7007158647148031E-2</v>
       </c>
       <c r="N26" s="3">
-        <v>0.0871123231191383</v>
+        <v>8.7112323119138302E-2</v>
       </c>
       <c r="Q26" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
@@ -11344,10 +11411,10 @@
         <v>1202</v>
       </c>
       <c r="I27" s="3">
-        <v>-0.02975721577329286</v>
+        <v>-2.975721577329286E-2</v>
       </c>
       <c r="J27" s="4">
-        <v>0.3904148177679194</v>
+        <v>0.39041481776791942</v>
       </c>
       <c r="K27" s="5">
         <v>782</v>
@@ -11356,7 +11423,7 @@
         <v>0.1473903000749337</v>
       </c>
       <c r="M27" s="3">
-        <v>0.1284186182703183</v>
+        <v>0.12841861827031831</v>
       </c>
       <c r="N27" s="3">
         <v>0.1287165632744256</v>
@@ -11365,7 +11432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -11379,10 +11446,10 @@
         <v>1202</v>
       </c>
       <c r="I28" s="3">
-        <v>-0.004032491910209131</v>
+        <v>-4.0324919102091312E-3</v>
       </c>
       <c r="J28" s="4">
-        <v>0.9050685397998213</v>
+        <v>0.90506853979982127</v>
       </c>
       <c r="K28" s="5">
         <v>783</v>
@@ -11391,16 +11458,16 @@
         <v>0.2013849635250253</v>
       </c>
       <c r="M28" s="3">
-        <v>0.1836379627144704</v>
+        <v>0.18363796271447039</v>
       </c>
       <c r="N28" s="3">
-        <v>0.1846885411198002</v>
+        <v>0.18468854111980021</v>
       </c>
       <c r="Q28" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -11414,28 +11481,28 @@
         <v>1202</v>
       </c>
       <c r="I29" s="3">
-        <v>0.0261213035366421</v>
+        <v>2.6121303536642101E-2</v>
       </c>
       <c r="J29" s="4">
-        <v>0.4731463916352461</v>
+        <v>0.47314639163524608</v>
       </c>
       <c r="K29" s="5">
         <v>784</v>
       </c>
       <c r="L29" s="3">
-        <v>0.06657959939398961</v>
+        <v>6.6579599393989608E-2</v>
       </c>
       <c r="M29" s="3">
-        <v>0.04710798738656308</v>
+        <v>4.7107987386563077E-2</v>
       </c>
       <c r="N29" s="3">
-        <v>0.04770959120423857</v>
+        <v>4.7709591204238573E-2</v>
       </c>
       <c r="Q29" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -11449,10 +11516,10 @@
         <v>1203</v>
       </c>
       <c r="I30" s="3">
-        <v>0.02824556989360839</v>
+        <v>2.824556989360839E-2</v>
       </c>
       <c r="J30" s="4">
-        <v>0.4263780093617003</v>
+        <v>0.42637800936170028</v>
       </c>
       <c r="K30" s="5">
         <v>781</v>
@@ -11461,16 +11528,16 @@
         <v>0.1174537729566115</v>
       </c>
       <c r="M30" s="3">
-        <v>0.09779022661357406</v>
+        <v>9.7790226613574061E-2</v>
       </c>
       <c r="N30" s="3">
-        <v>0.09822320892236236</v>
+        <v>9.8223208922362359E-2</v>
       </c>
       <c r="Q30" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -11484,10 +11551,10 @@
         <v>1203</v>
       </c>
       <c r="I31" s="3">
-        <v>-0.02309383120173522</v>
+        <v>-2.3093831201735221E-2</v>
       </c>
       <c r="J31" s="4">
-        <v>0.4991979179084282</v>
+        <v>0.49919791790842821</v>
       </c>
       <c r="K31" s="5">
         <v>782</v>
@@ -11499,13 +11566,13 @@
         <v>0.1518545782473322</v>
       </c>
       <c r="N31" s="3">
-        <v>0.1524565100588259</v>
+        <v>0.15245651005882591</v>
       </c>
       <c r="Q31" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
@@ -11519,7 +11586,7 @@
         <v>1203</v>
       </c>
       <c r="I32" s="3">
-        <v>0.0236817855765428</v>
+        <v>2.36817855765428E-2</v>
       </c>
       <c r="J32" s="4">
         <v>0.4468631206819863</v>
@@ -11528,19 +11595,19 @@
         <v>783</v>
       </c>
       <c r="L32" s="3">
-        <v>0.3231681150993873</v>
+        <v>0.32316811509938731</v>
       </c>
       <c r="M32" s="3">
-        <v>0.3081274065460403</v>
+        <v>0.30812740654604032</v>
       </c>
       <c r="N32" s="3">
-        <v>0.3085074906910465</v>
+        <v>0.30850749069104649</v>
       </c>
       <c r="Q32" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -11554,10 +11621,10 @@
         <v>1203</v>
       </c>
       <c r="I33" s="3">
-        <v>0.0216341881394921</v>
+        <v>2.1634188139492101E-2</v>
       </c>
       <c r="J33" s="4">
-        <v>0.5443165721215386</v>
+        <v>0.54431657212153861</v>
       </c>
       <c r="K33" s="5">
         <v>784</v>
@@ -11566,16 +11633,16 @@
         <v>0.1035567285581888</v>
       </c>
       <c r="M33" s="3">
-        <v>0.08485647778495675</v>
+        <v>8.4856477784956752E-2</v>
       </c>
       <c r="N33" s="3">
-        <v>0.08560965310718738</v>
+        <v>8.5609653107187378E-2</v>
       </c>
       <c r="Q33" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
@@ -11589,46 +11656,46 @@
         <v>1202</v>
       </c>
       <c r="E34" s="3">
-        <v>-0.3639477141561612</v>
+        <v>-0.36394771415616117</v>
       </c>
       <c r="F34" s="4">
-        <v>2.681452516045822E-88</v>
+        <v>2.6814525160458219E-88</v>
       </c>
       <c r="G34" s="3">
-        <v>-0.7826154707239186</v>
+        <v>-0.78261547072391857</v>
       </c>
       <c r="H34" s="4">
-        <v>0.03739902614748261</v>
+        <v>3.7399026147482611E-2</v>
       </c>
       <c r="I34" s="3">
-        <v>-0.4186677565677575</v>
+        <v>-0.41866775656775751</v>
       </c>
       <c r="J34" s="4">
-        <v>0.2657254811900062</v>
+        <v>0.26572548119000622</v>
       </c>
       <c r="K34" s="5">
         <v>2385</v>
       </c>
       <c r="L34" s="3">
-        <v>0.3181388680021791</v>
+        <v>0.31813886800217911</v>
       </c>
       <c r="M34" s="3">
-        <v>0.3114964258014379</v>
+        <v>0.31149642580143788</v>
       </c>
       <c r="N34" s="3">
-        <v>0.3114266811213381</v>
+        <v>0.31142668112133809</v>
       </c>
       <c r="O34" s="3">
         <v>-1.51953881178635</v>
       </c>
       <c r="P34" s="3">
-        <v>-0.04569212966148695</v>
+        <v>-4.5692129661486947E-2</v>
       </c>
       <c r="Q34" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -11648,40 +11715,40 @@
         <v>1.410482812302159E-10</v>
       </c>
       <c r="G35" s="3">
-        <v>-6.735765369988814</v>
+        <v>-6.7357653699888136</v>
       </c>
       <c r="H35" s="4">
-        <v>1.289988303121556E-09</v>
+        <v>1.289988303121556E-9</v>
       </c>
       <c r="I35" s="3">
-        <v>-6.612360207200463</v>
+        <v>-6.6123602072004628</v>
       </c>
       <c r="J35" s="4">
-        <v>2.613113375993515E-09</v>
+        <v>2.6131133759935152E-9</v>
       </c>
       <c r="K35" s="5">
         <v>2426</v>
       </c>
       <c r="L35" s="3">
-        <v>0.202994890487927</v>
+        <v>0.20299489048792699</v>
       </c>
       <c r="M35" s="3">
-        <v>0.1953632845267372</v>
+        <v>0.19536328452673721</v>
       </c>
       <c r="N35" s="3">
         <v>0.1837363433404442</v>
       </c>
       <c r="O35" s="3">
-        <v>-8.903720703213649</v>
+        <v>-8.9037207032136489</v>
       </c>
       <c r="P35" s="3">
-        <v>-4.567810036763978</v>
+        <v>-4.5678100367639782</v>
       </c>
       <c r="Q35" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
@@ -11695,22 +11762,22 @@
         <v>1202</v>
       </c>
       <c r="E36" s="3">
-        <v>0.0757822823819858</v>
+        <v>7.5782282381985797E-2</v>
       </c>
       <c r="F36" s="4">
-        <v>5.376404711498543E-05</v>
+        <v>5.3764047114985432E-5</v>
       </c>
       <c r="G36" s="3">
-        <v>-8.171653859574263</v>
+        <v>-8.1716538595742634</v>
       </c>
       <c r="H36" s="4">
-        <v>5.933503889458099E-14</v>
+        <v>5.9335038894580989E-14</v>
       </c>
       <c r="I36" s="3">
-        <v>-8.24743614195625</v>
+        <v>-8.2474361419562499</v>
       </c>
       <c r="J36" s="4">
-        <v>3.587367606341387E-14</v>
+        <v>3.5873676063413868E-14</v>
       </c>
       <c r="K36" s="5">
         <v>2438</v>
@@ -11719,7 +11786,7 @@
         <v>0.1858506215135716</v>
       </c>
       <c r="M36" s="3">
-        <v>0.1780936058941897</v>
+        <v>0.17809360589418971</v>
       </c>
       <c r="N36" s="3">
         <v>0.1586665398747418</v>
@@ -11728,13 +11795,13 @@
         <v>-10.29282512903549</v>
       </c>
       <c r="P36" s="3">
-        <v>-6.050482590113038</v>
+        <v>-6.0504825901130381</v>
       </c>
       <c r="Q36" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
@@ -11748,46 +11815,46 @@
         <v>1202</v>
       </c>
       <c r="E37" s="3">
-        <v>-0.0004513883113511887</v>
+        <v>-4.513883113511887E-4</v>
       </c>
       <c r="F37" s="4">
-        <v>0.9789964387484922</v>
+        <v>0.97899643874849218</v>
       </c>
       <c r="G37" s="3">
-        <v>-6.011678392912851</v>
+        <v>-6.0116783929128514</v>
       </c>
       <c r="H37" s="4">
-        <v>7.308755324989103E-14</v>
+        <v>7.3087553249891028E-14</v>
       </c>
       <c r="I37" s="3">
-        <v>-6.0112270046015</v>
+        <v>-6.0112270046015004</v>
       </c>
       <c r="J37" s="4">
-        <v>7.645165398680639E-14</v>
+        <v>7.6451653986806393E-14</v>
       </c>
       <c r="K37" s="5">
         <v>2423</v>
       </c>
       <c r="L37" s="3">
-        <v>0.3131130638340671</v>
+        <v>0.31311306383406712</v>
       </c>
       <c r="M37" s="3">
-        <v>0.306816600252546</v>
+        <v>0.30681660025254598</v>
       </c>
       <c r="N37" s="3">
-        <v>0.2907752982017044</v>
+        <v>0.29077529820170439</v>
       </c>
       <c r="O37" s="3">
-        <v>-7.577889322717706</v>
+        <v>-7.5778893227177058</v>
       </c>
       <c r="P37" s="3">
-        <v>-4.445467463107997</v>
+        <v>-4.4454674631079971</v>
       </c>
       <c r="Q37" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
@@ -11801,34 +11868,34 @@
         <v>1203</v>
       </c>
       <c r="E38" s="3">
-        <v>-0.04243588919203595</v>
+        <v>-4.2435889192035947E-2</v>
       </c>
       <c r="F38" s="4">
-        <v>0.03442075618405321</v>
+        <v>3.4420756184053207E-2</v>
       </c>
       <c r="G38" s="3">
-        <v>-0.3555940322566353</v>
+        <v>-0.35559403225663527</v>
       </c>
       <c r="H38" s="4">
-        <v>0.4088337388172741</v>
+        <v>0.40883373881727408</v>
       </c>
       <c r="I38" s="3">
-        <v>-0.3131581430645994</v>
+        <v>-0.31315814306459938</v>
       </c>
       <c r="J38" s="4">
-        <v>0.46732939358544</v>
+        <v>0.46732939358544001</v>
       </c>
       <c r="K38" s="5">
         <v>2385</v>
       </c>
       <c r="L38" s="3">
-        <v>0.1053731104890648</v>
+        <v>0.10537311048906479</v>
       </c>
       <c r="M38" s="3">
-        <v>0.09665798195930975</v>
+        <v>9.6657981959309747E-2</v>
       </c>
       <c r="N38" s="3">
-        <v>0.09683832354171318</v>
+        <v>9.6838323541713178E-2</v>
       </c>
       <c r="O38" s="3">
         <v>-1.199696788959306</v>
@@ -11840,7 +11907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -11854,31 +11921,31 @@
         <v>1203</v>
       </c>
       <c r="E39" s="3">
-        <v>-0.1213749885920301</v>
+        <v>-0.12137498859203009</v>
       </c>
       <c r="F39" s="4">
-        <v>3.818703119818921E-10</v>
+        <v>3.8187031198189211E-10</v>
       </c>
       <c r="G39" s="3">
         <v>-3.40291692177352</v>
       </c>
       <c r="H39" s="4">
-        <v>0.002283077373144845</v>
+        <v>2.283077373144845E-3</v>
       </c>
       <c r="I39" s="3">
-        <v>-3.28154193318149</v>
+        <v>-3.2815419331814901</v>
       </c>
       <c r="J39" s="4">
-        <v>0.003281349981122145</v>
+        <v>3.2813499811221451E-3</v>
       </c>
       <c r="K39" s="5">
         <v>2426</v>
       </c>
       <c r="L39" s="3">
-        <v>0.1904091066623667</v>
+        <v>0.19040910666236671</v>
       </c>
       <c r="M39" s="3">
-        <v>0.1826569873672935</v>
+        <v>0.18265698736729349</v>
       </c>
       <c r="N39" s="3">
         <v>0.1800510792887742</v>
@@ -11887,13 +11954,13 @@
         <v>-5.58792267329593</v>
       </c>
       <c r="P39" s="3">
-        <v>-1.21791117025111</v>
+        <v>-1.2179111702511101</v>
       </c>
       <c r="Q39" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
@@ -11907,46 +11974,46 @@
         <v>1203</v>
       </c>
       <c r="E40" s="3">
-        <v>0.03840067323141881</v>
+        <v>3.8400673231418811E-2</v>
       </c>
       <c r="F40" s="4">
-        <v>0.04480446588571344</v>
+        <v>4.4804465885713442E-2</v>
       </c>
       <c r="G40" s="3">
         <v>-1.626445382033997</v>
       </c>
       <c r="H40" s="4">
-        <v>0.1410601462723026</v>
+        <v>0.14106014627230259</v>
       </c>
       <c r="I40" s="3">
-        <v>-1.664846055265416</v>
+        <v>-1.6648460552654161</v>
       </c>
       <c r="J40" s="4">
-        <v>0.1320822996489283</v>
+        <v>0.13208229964892829</v>
       </c>
       <c r="K40" s="5">
         <v>2438</v>
       </c>
       <c r="L40" s="3">
-        <v>0.1509198390419471</v>
+        <v>0.15091983904194711</v>
       </c>
       <c r="M40" s="3">
-        <v>0.1428300114934651</v>
+        <v>0.14283001149346511</v>
       </c>
       <c r="N40" s="3">
-        <v>0.1423794579825914</v>
+        <v>0.14237945798259141</v>
       </c>
       <c r="O40" s="3">
         <v>-3.792642806114094</v>
       </c>
       <c r="P40" s="3">
-        <v>0.5397520420460999</v>
+        <v>0.53975204204609994</v>
       </c>
       <c r="Q40" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
@@ -11960,37 +12027,37 @@
         <v>1203</v>
       </c>
       <c r="E41" s="3">
-        <v>0.02642742064472006</v>
+        <v>2.6427420644720059E-2</v>
       </c>
       <c r="F41" s="4">
         <v>0.1319714324748576</v>
       </c>
       <c r="G41" s="3">
-        <v>-2.782630719703947</v>
+        <v>-2.7826307197039468</v>
       </c>
       <c r="H41" s="4">
-        <v>0.0006709239733194354</v>
+        <v>6.7092397331943538E-4</v>
       </c>
       <c r="I41" s="3">
-        <v>-2.809058140348667</v>
+        <v>-2.8090581403486672</v>
       </c>
       <c r="J41" s="4">
-        <v>0.0006015061289609142</v>
+        <v>6.0150612896091424E-4</v>
       </c>
       <c r="K41" s="5">
         <v>2423</v>
       </c>
       <c r="L41" s="3">
-        <v>0.2811638626948462</v>
+        <v>0.28116386269484622</v>
       </c>
       <c r="M41" s="3">
-        <v>0.2745745314362155</v>
+        <v>0.27457453143621552</v>
       </c>
       <c r="N41" s="3">
-        <v>0.2713106640076243</v>
+        <v>0.27131066400762432</v>
       </c>
       <c r="O41" s="3">
-        <v>-4.384852285269081</v>
+        <v>-4.3848522852690808</v>
       </c>
       <c r="P41" s="3">
         <v>-1.180409154138814</v>
@@ -11999,7 +12066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
@@ -12013,19 +12080,19 @@
         <v>1202</v>
       </c>
       <c r="E42" s="3">
-        <v>-0.03920431550106062</v>
+        <v>-3.920431550106062E-2</v>
       </c>
       <c r="F42" s="4">
-        <v>0.165137131322823</v>
+        <v>0.16513713132282301</v>
       </c>
       <c r="G42" s="3">
         <v>-0.111934862658447</v>
       </c>
       <c r="H42" s="4">
-        <v>0.04876340090525957</v>
+        <v>4.8763400905259567E-2</v>
       </c>
       <c r="I42" s="3">
-        <v>-0.07273054715738633</v>
+        <v>-7.2730547157386333E-2</v>
       </c>
       <c r="J42" s="4">
         <v>0.2258486845677023</v>
@@ -12034,25 +12101,25 @@
         <v>1786</v>
       </c>
       <c r="L42" s="3">
-        <v>0.07002122079649165</v>
+        <v>7.0021220796491646E-2</v>
       </c>
       <c r="M42" s="3">
-        <v>0.05788188372402803</v>
+        <v>5.7881883724028027E-2</v>
       </c>
       <c r="N42" s="3">
-        <v>0.05763187581639606</v>
+        <v>5.7631875816396061E-2</v>
       </c>
       <c r="O42" s="3">
         <v>-0.2232618271255048</v>
       </c>
       <c r="P42" s="3">
-        <v>-0.0006078981913891085</v>
+        <v>-6.078981913891085E-4</v>
       </c>
       <c r="Q42" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -12066,22 +12133,22 @@
         <v>1202</v>
       </c>
       <c r="E43" s="3">
-        <v>-0.0289762284546432</v>
+        <v>-2.8976228454643201E-2</v>
       </c>
       <c r="F43" s="4">
         <v>0.273444284642612</v>
       </c>
       <c r="G43" s="3">
-        <v>0.005929770513695278</v>
+        <v>5.9297705136952782E-3</v>
       </c>
       <c r="H43" s="4">
-        <v>0.9197492412338868</v>
+        <v>0.91974924123388679</v>
       </c>
       <c r="I43" s="3">
-        <v>0.03490599896833848</v>
+        <v>3.4905998968338479E-2</v>
       </c>
       <c r="J43" s="4">
-        <v>0.5743162165198641</v>
+        <v>0.57431621651986409</v>
       </c>
       <c r="K43" s="5">
         <v>1791</v>
@@ -12090,10 +12157,10 @@
         <v>0.1056335111347676</v>
       </c>
       <c r="M43" s="3">
-        <v>0.09399206843872887</v>
+        <v>9.3992068438728871E-2</v>
       </c>
       <c r="N43" s="3">
-        <v>0.09434277174839001</v>
+        <v>9.4342771748390009E-2</v>
       </c>
       <c r="O43" s="3">
         <v>-0.1094894629751566</v>
@@ -12105,7 +12172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>5</v>
       </c>
@@ -12119,22 +12186,22 @@
         <v>1202</v>
       </c>
       <c r="E44" s="3">
-        <v>0.06708117939277561</v>
+        <v>6.7081179392775608E-2</v>
       </c>
       <c r="F44" s="4">
-        <v>0.01707523337278739</v>
+        <v>1.707523337278739E-2</v>
       </c>
       <c r="G44" s="3">
-        <v>0.0771099898952228</v>
+        <v>7.7109989895222802E-2</v>
       </c>
       <c r="H44" s="4">
-        <v>0.06516551361335549</v>
+        <v>6.5165513613355486E-2</v>
       </c>
       <c r="I44" s="3">
-        <v>0.0100288105024472</v>
+        <v>1.0028810502447199E-2</v>
       </c>
       <c r="J44" s="4">
-        <v>0.8367386566923657</v>
+        <v>0.83673865669236569</v>
       </c>
       <c r="K44" s="5">
         <v>1795</v>
@@ -12146,19 +12213,19 @@
         <v>0.1292183689693486</v>
       </c>
       <c r="N44" s="3">
-        <v>0.1296889074871412</v>
+        <v>0.12968890748714121</v>
       </c>
       <c r="O44" s="3">
-        <v>-0.004848956084044703</v>
+        <v>-4.8489560840447032E-3</v>
       </c>
       <c r="P44" s="3">
-        <v>0.1590689358744903</v>
+        <v>0.15906893587449031</v>
       </c>
       <c r="Q44" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
@@ -12172,46 +12239,46 @@
         <v>1202</v>
       </c>
       <c r="E45" s="3">
-        <v>0.06051797403654564</v>
+        <v>6.0517974036545637E-2</v>
       </c>
       <c r="F45" s="4">
-        <v>0.03178771868273421</v>
+        <v>3.1787718682734209E-2</v>
       </c>
       <c r="G45" s="3">
-        <v>0.07464578419660831</v>
+        <v>7.4645784196608306E-2</v>
       </c>
       <c r="H45" s="4">
-        <v>0.1882372653340267</v>
+        <v>0.18823726533402671</v>
       </c>
       <c r="I45" s="3">
-        <v>0.01412781016006267</v>
+        <v>1.4127810160062671E-2</v>
       </c>
       <c r="J45" s="4">
-        <v>0.8139257857005402</v>
+        <v>0.81392578570054019</v>
       </c>
       <c r="K45" s="5">
         <v>1794</v>
       </c>
       <c r="L45" s="3">
-        <v>0.06507484096738125</v>
+        <v>6.5074840967381253E-2</v>
       </c>
       <c r="M45" s="3">
-        <v>0.05346086383654125</v>
+        <v>5.346086383654125E-2</v>
       </c>
       <c r="N45" s="3">
-        <v>0.05396542849478159</v>
+        <v>5.3965428494781587E-2</v>
       </c>
       <c r="O45" s="3">
-        <v>-0.03657579901387713</v>
+        <v>-3.6575799013877128E-2</v>
       </c>
       <c r="P45" s="3">
-        <v>0.1858673674070938</v>
+        <v>0.18586736740709381</v>
       </c>
       <c r="Q45" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
@@ -12225,46 +12292,46 @@
         <v>1203</v>
       </c>
       <c r="E46" s="3">
-        <v>-0.03512394385394942</v>
+        <v>-3.5123943853949423E-2</v>
       </c>
       <c r="F46" s="4">
         <v>0.2130032015158568</v>
       </c>
       <c r="G46" s="3">
-        <v>-0.08933209240564172</v>
+        <v>-8.9332092405641716E-2</v>
       </c>
       <c r="H46" s="4">
-        <v>0.1151995773697699</v>
+        <v>0.11519957736976991</v>
       </c>
       <c r="I46" s="3">
-        <v>-0.0542081485516923</v>
+        <v>-5.4208148551692301E-2</v>
       </c>
       <c r="J46" s="4">
-        <v>0.3659770708424016</v>
+        <v>0.36597707084240161</v>
       </c>
       <c r="K46" s="5">
         <v>1786</v>
       </c>
       <c r="L46" s="3">
-        <v>0.07262752587927757</v>
+        <v>7.2627525879277566E-2</v>
       </c>
       <c r="M46" s="3">
-        <v>0.06052220981527257</v>
+        <v>6.0522209815272572E-2</v>
       </c>
       <c r="N46" s="3">
-        <v>0.06061935484355296</v>
+        <v>6.0619354843552957E-2</v>
       </c>
       <c r="O46" s="3">
-        <v>-0.2005029481441707</v>
+        <v>-0.20050294814417069</v>
       </c>
       <c r="P46" s="3">
-        <v>0.02183876333288726</v>
+        <v>2.183876333288726E-2</v>
       </c>
       <c r="Q46" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
@@ -12278,31 +12345,31 @@
         <v>1203</v>
       </c>
       <c r="E47" s="3">
-        <v>-0.03238617408519421</v>
+        <v>-3.238617408519421E-2</v>
       </c>
       <c r="F47" s="4">
         <v>0.2124522986553001</v>
       </c>
       <c r="G47" s="3">
-        <v>0.002720521070931625</v>
+        <v>2.7205210709316252E-3</v>
       </c>
       <c r="H47" s="4">
-        <v>0.9624442504673726</v>
+        <v>0.96244425046737259</v>
       </c>
       <c r="I47" s="3">
-        <v>0.03510669515612583</v>
+        <v>3.5106695156125828E-2</v>
       </c>
       <c r="J47" s="4">
-        <v>0.5649606938611647</v>
+        <v>0.56496069386116465</v>
       </c>
       <c r="K47" s="5">
         <v>1791</v>
       </c>
       <c r="L47" s="3">
-        <v>0.1381377531167675</v>
+        <v>0.13813775311676749</v>
       </c>
       <c r="M47" s="3">
-        <v>0.1269193990260405</v>
+        <v>0.12691939902604049</v>
       </c>
       <c r="N47" s="3">
         <v>0.127249612993205</v>
@@ -12311,13 +12378,13 @@
         <v>-0.1105819431093337</v>
       </c>
       <c r="P47" s="3">
-        <v>0.1160229852511969</v>
+        <v>0.11602298525119691</v>
       </c>
       <c r="Q47" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>5</v>
       </c>
@@ -12331,22 +12398,22 @@
         <v>1203</v>
       </c>
       <c r="E48" s="3">
-        <v>0.09599747864773653</v>
+        <v>9.5997478647736528E-2</v>
       </c>
       <c r="F48" s="4">
-        <v>0.0004536520689239476</v>
+        <v>4.5365206892394758E-4</v>
       </c>
       <c r="G48" s="3">
-        <v>0.04059632133123467</v>
+        <v>4.0596321331234669E-2</v>
       </c>
       <c r="H48" s="4">
         <v>0.3179147203092697</v>
       </c>
       <c r="I48" s="3">
-        <v>-0.05540115731650186</v>
+        <v>-5.5401157316501859E-2</v>
       </c>
       <c r="J48" s="4">
-        <v>0.2418326028131502</v>
+        <v>0.24183260281315019</v>
       </c>
       <c r="K48" s="5">
         <v>1795</v>
@@ -12355,22 +12422,22 @@
         <v>0.1871404390478624</v>
       </c>
       <c r="M48" s="3">
-        <v>0.1765838213731594</v>
+        <v>0.17658382137315939</v>
       </c>
       <c r="N48" s="3">
         <v>0.1764115190101091</v>
       </c>
       <c r="O48" s="3">
-        <v>-0.03910241453888395</v>
+        <v>-3.9102414538883953E-2</v>
       </c>
       <c r="P48" s="3">
-        <v>0.1202950572013533</v>
+        <v>0.12029505720135331</v>
       </c>
       <c r="Q48" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
@@ -12384,37 +12451,37 @@
         <v>1203</v>
       </c>
       <c r="E49" s="3">
-        <v>0.06962295298077759</v>
+        <v>6.9622952980777586E-2</v>
       </c>
       <c r="F49" s="4">
-        <v>0.01344223752446459</v>
+        <v>1.3442237524464591E-2</v>
       </c>
       <c r="G49" s="3">
-        <v>0.07777394150365061</v>
+        <v>7.7773941503650607E-2</v>
       </c>
       <c r="H49" s="4">
-        <v>0.1700083371983341</v>
+        <v>0.17000833719833411</v>
       </c>
       <c r="I49" s="3">
-        <v>0.008150988522873017</v>
+        <v>8.1509885228730171E-3</v>
       </c>
       <c r="J49" s="4">
-        <v>0.8918864319150244</v>
+        <v>0.89188643191502437</v>
       </c>
       <c r="K49" s="5">
         <v>1794</v>
       </c>
       <c r="L49" s="3">
-        <v>0.06678204358301498</v>
+        <v>6.6782043583014983E-2</v>
       </c>
       <c r="M49" s="3">
-        <v>0.05518927393808348</v>
+        <v>5.5189273938083483E-2</v>
       </c>
       <c r="N49" s="3">
-        <v>0.05571261008937101</v>
+        <v>5.5712610089371013E-2</v>
       </c>
       <c r="O49" s="3">
-        <v>-0.03334604826063224</v>
+        <v>-3.3346048260632241E-2</v>
       </c>
       <c r="P49" s="3">
         <v>0.1888939312679335</v>
@@ -12424,7 +12491,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q49"/>
+  <autoFilter ref="A1:Q49" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>